--- a/jpcore-r4/develop/StructureDefinition-jp-common-department.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-common-department.xlsx
@@ -268,7 +268,8 @@
     <t>診療科情報は以下の2つの方法で表現できる：
 1. valueCodeableConcept: SS-MIX2診療科コードなどのコード化された診療科情報
 2. valueReference: JP_Organization_Departmentプロファイルを使用した診療科組織への参照
-用途に応じて適切な表現方法を選択すること。診療科名称の統一が困難な場合は、CodeableConceptのtext要素を使用してテキストベースで診療科名を記録することも可能。</t>
+用途に応じて適切な表現方法を選択すること。診療科名称の統一が困難な場合は、CodeableConceptのtext要素を使用してテキストベースで診療科名を記録することも可能。
+【適用コンテキストについて】本拡張の適用コンテキスト（^context）は意図的に `Resource`（全リソース）を指定し、広い範囲での参照を前提としている。これは、日本の医療制度上、診療科という項目の必要性が高く、診療・検査・処方・予約・実施組織など多様なリソースが診療科情報を保持しうること、また多くの医療情報システムのデータベーステーブルに診療科コードが項目として記載されていることによる。適用先リソース型を限定列挙すると将来の利用箇所を制約しかねないため、汎用拡張として全リソースで利用可能とすることを優先している。なお、コンテキストが広いことにより IPS validator 等で「コンテキストが広すぎる」旨の警告（情報レベル）が出る場合があるが、上記の設計意図に基づく許容事項である。</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
